--- a/template/shuro_youshiki.xlsx
+++ b/template/shuro_youshiki.xlsx
@@ -9,6 +9,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="別紙１" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表１" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表４" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="別紙３" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="別紙４" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'別紙１'!$A$1:$F$64</definedName>
@@ -22,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\-#,##0;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
@@ -243,6 +245,10 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -258,7 +264,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -600,6 +606,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="14">
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1">
@@ -639,7 +692,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1379,6 +1432,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3489,14 +3559,9 @@
       <c r="N19" s="23" t="n"/>
       <c r="O19" s="23" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="C21" s="186" t="n"/>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="D26" s="30" t="n"/>
     </row>
@@ -4475,4 +4540,530 @@
   <pageMargins left="0.5" right="0.23" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" style="237" min="1" max="1"/>
+    <col width="14" customWidth="1" style="237" min="2" max="2"/>
+    <col width="16" customWidth="1" style="237" min="3" max="3"/>
+    <col width="16" customWidth="1" style="237" min="4" max="4"/>
+    <col width="16" customWidth="1" style="237" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>（別紙３）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="253" t="inlineStr">
+        <is>
+          <t>その他の積立金明細表</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="254" t="inlineStr">
+        <is>
+          <t>自　令和　年　月　日　至　令和　年　月　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="255" t="inlineStr">
+        <is>
+          <t>積立金の種類等</t>
+        </is>
+      </c>
+      <c r="B5" s="255" t="n"/>
+      <c r="C5" s="255" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="D5" s="255" t="inlineStr">
+        <is>
+          <t>事業所計</t>
+        </is>
+      </c>
+      <c r="E5" s="255" t="inlineStr">
+        <is>
+          <t>就労継続支援Ｂ型</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="255" t="inlineStr">
+        <is>
+          <t>工賃変動積立金</t>
+        </is>
+      </c>
+      <c r="B6" s="256" t="inlineStr">
+        <is>
+          <t>前期繰越額</t>
+        </is>
+      </c>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="258" t="n"/>
+      <c r="B7" s="256" t="inlineStr">
+        <is>
+          <t>当期積立額</t>
+        </is>
+      </c>
+      <c r="C7" s="257" t="n"/>
+      <c r="D7" s="257" t="n"/>
+      <c r="E7" s="257" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="258" t="n"/>
+      <c r="B8" s="256" t="inlineStr">
+        <is>
+          <t>当期取崩額</t>
+        </is>
+      </c>
+      <c r="C8" s="257" t="n"/>
+      <c r="D8" s="257" t="n"/>
+      <c r="E8" s="257" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="259" t="n"/>
+      <c r="B9" s="256" t="inlineStr">
+        <is>
+          <t>当期末残高</t>
+        </is>
+      </c>
+      <c r="C9" s="257" t="n"/>
+      <c r="D9" s="257" t="n"/>
+      <c r="E9" s="257" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="255" t="inlineStr">
+        <is>
+          <t>設備等整備積立金</t>
+        </is>
+      </c>
+      <c r="B10" s="256" t="inlineStr">
+        <is>
+          <t>前期繰越額</t>
+        </is>
+      </c>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="258" t="n"/>
+      <c r="B11" s="256" t="inlineStr">
+        <is>
+          <t>当期積立額</t>
+        </is>
+      </c>
+      <c r="C11" s="257" t="n"/>
+      <c r="D11" s="257" t="n"/>
+      <c r="E11" s="257" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="258" t="n"/>
+      <c r="B12" s="256" t="inlineStr">
+        <is>
+          <t>当期取崩額</t>
+        </is>
+      </c>
+      <c r="C12" s="257" t="n"/>
+      <c r="D12" s="257" t="n"/>
+      <c r="E12" s="257" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="259" t="n"/>
+      <c r="B13" s="256" t="inlineStr">
+        <is>
+          <t>当期末残高</t>
+        </is>
+      </c>
+      <c r="C13" s="257" t="n"/>
+      <c r="D13" s="257" t="n"/>
+      <c r="E13" s="257" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="255" t="inlineStr"/>
+      <c r="B14" s="256" t="inlineStr">
+        <is>
+          <t>前期繰越額</t>
+        </is>
+      </c>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="258" t="n"/>
+      <c r="B15" s="256" t="inlineStr">
+        <is>
+          <t>当期積立額</t>
+        </is>
+      </c>
+      <c r="C15" s="257" t="n"/>
+      <c r="D15" s="257" t="n"/>
+      <c r="E15" s="257" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="258" t="n"/>
+      <c r="B16" s="256" t="inlineStr">
+        <is>
+          <t>当期取崩額</t>
+        </is>
+      </c>
+      <c r="C16" s="257" t="n"/>
+      <c r="D16" s="257" t="n"/>
+      <c r="E16" s="257" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="259" t="n"/>
+      <c r="B17" s="256" t="inlineStr">
+        <is>
+          <t>当期末残高</t>
+        </is>
+      </c>
+      <c r="C17" s="257" t="n"/>
+      <c r="D17" s="257" t="n"/>
+      <c r="E17" s="257" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="255" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B18" s="256" t="inlineStr">
+        <is>
+          <t>前期繰越額</t>
+        </is>
+      </c>
+      <c r="C18" s="257" t="n"/>
+      <c r="D18" s="257" t="n"/>
+      <c r="E18" s="257" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="258" t="n"/>
+      <c r="B19" s="256" t="inlineStr">
+        <is>
+          <t>当期積立額</t>
+        </is>
+      </c>
+      <c r="C19" s="257" t="n"/>
+      <c r="D19" s="257" t="n"/>
+      <c r="E19" s="257" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="258" t="n"/>
+      <c r="B20" s="256" t="inlineStr">
+        <is>
+          <t>当期取崩額</t>
+        </is>
+      </c>
+      <c r="C20" s="257" t="n"/>
+      <c r="D20" s="257" t="n"/>
+      <c r="E20" s="257" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="259" t="n"/>
+      <c r="B21" s="256" t="inlineStr">
+        <is>
+          <t>当期末残高</t>
+        </is>
+      </c>
+      <c r="C21" s="257" t="n"/>
+      <c r="D21" s="257" t="n"/>
+      <c r="E21" s="257" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" style="237" min="1" max="1"/>
+    <col width="14" customWidth="1" style="237" min="2" max="2"/>
+    <col width="16" customWidth="1" style="237" min="3" max="3"/>
+    <col width="16" customWidth="1" style="237" min="4" max="4"/>
+    <col width="16" customWidth="1" style="237" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>（別紙４）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="253" t="inlineStr">
+        <is>
+          <t>その他の積立資産明細表</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="254" t="inlineStr">
+        <is>
+          <t>自　令和　年　月　日　至　令和　年　月　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="255" t="inlineStr">
+        <is>
+          <t>積立資産の種類等</t>
+        </is>
+      </c>
+      <c r="B5" s="255" t="n"/>
+      <c r="C5" s="255" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="D5" s="255" t="inlineStr">
+        <is>
+          <t>事業所計</t>
+        </is>
+      </c>
+      <c r="E5" s="255" t="inlineStr">
+        <is>
+          <t>就労継続支援Ｂ型</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="255" t="inlineStr">
+        <is>
+          <t>工賃変動積立資産</t>
+        </is>
+      </c>
+      <c r="B6" s="256" t="inlineStr">
+        <is>
+          <t>前期繰越額</t>
+        </is>
+      </c>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="258" t="n"/>
+      <c r="B7" s="256" t="inlineStr">
+        <is>
+          <t>当期積立額</t>
+        </is>
+      </c>
+      <c r="C7" s="257" t="n"/>
+      <c r="D7" s="257" t="n"/>
+      <c r="E7" s="257" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="258" t="n"/>
+      <c r="B8" s="256" t="inlineStr">
+        <is>
+          <t>当期取崩額</t>
+        </is>
+      </c>
+      <c r="C8" s="257" t="n"/>
+      <c r="D8" s="257" t="n"/>
+      <c r="E8" s="257" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="259" t="n"/>
+      <c r="B9" s="256" t="inlineStr">
+        <is>
+          <t>当期末残高</t>
+        </is>
+      </c>
+      <c r="C9" s="257" t="n"/>
+      <c r="D9" s="257" t="n"/>
+      <c r="E9" s="257" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="255" t="inlineStr">
+        <is>
+          <t>設備等整備積立資産</t>
+        </is>
+      </c>
+      <c r="B10" s="256" t="inlineStr">
+        <is>
+          <t>前期繰越額</t>
+        </is>
+      </c>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="258" t="n"/>
+      <c r="B11" s="256" t="inlineStr">
+        <is>
+          <t>当期積立額</t>
+        </is>
+      </c>
+      <c r="C11" s="257" t="n"/>
+      <c r="D11" s="257" t="n"/>
+      <c r="E11" s="257" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="258" t="n"/>
+      <c r="B12" s="256" t="inlineStr">
+        <is>
+          <t>当期取崩額</t>
+        </is>
+      </c>
+      <c r="C12" s="257" t="n"/>
+      <c r="D12" s="257" t="n"/>
+      <c r="E12" s="257" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="259" t="n"/>
+      <c r="B13" s="256" t="inlineStr">
+        <is>
+          <t>当期末残高</t>
+        </is>
+      </c>
+      <c r="C13" s="257" t="n"/>
+      <c r="D13" s="257" t="n"/>
+      <c r="E13" s="257" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="255" t="inlineStr"/>
+      <c r="B14" s="256" t="inlineStr">
+        <is>
+          <t>前期繰越額</t>
+        </is>
+      </c>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="258" t="n"/>
+      <c r="B15" s="256" t="inlineStr">
+        <is>
+          <t>当期積立額</t>
+        </is>
+      </c>
+      <c r="C15" s="257" t="n"/>
+      <c r="D15" s="257" t="n"/>
+      <c r="E15" s="257" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="258" t="n"/>
+      <c r="B16" s="256" t="inlineStr">
+        <is>
+          <t>当期取崩額</t>
+        </is>
+      </c>
+      <c r="C16" s="257" t="n"/>
+      <c r="D16" s="257" t="n"/>
+      <c r="E16" s="257" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="259" t="n"/>
+      <c r="B17" s="256" t="inlineStr">
+        <is>
+          <t>当期末残高</t>
+        </is>
+      </c>
+      <c r="C17" s="257" t="n"/>
+      <c r="D17" s="257" t="n"/>
+      <c r="E17" s="257" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="255" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B18" s="256" t="inlineStr">
+        <is>
+          <t>前期繰越額</t>
+        </is>
+      </c>
+      <c r="C18" s="257" t="n"/>
+      <c r="D18" s="257" t="n"/>
+      <c r="E18" s="257" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="258" t="n"/>
+      <c r="B19" s="256" t="inlineStr">
+        <is>
+          <t>当期積立額</t>
+        </is>
+      </c>
+      <c r="C19" s="257" t="n"/>
+      <c r="D19" s="257" t="n"/>
+      <c r="E19" s="257" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="258" t="n"/>
+      <c r="B20" s="256" t="inlineStr">
+        <is>
+          <t>当期取崩額</t>
+        </is>
+      </c>
+      <c r="C20" s="257" t="n"/>
+      <c r="D20" s="257" t="n"/>
+      <c r="E20" s="257" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="259" t="n"/>
+      <c r="B21" s="256" t="inlineStr">
+        <is>
+          <t>当期末残高</t>
+        </is>
+      </c>
+      <c r="C21" s="257" t="n"/>
+      <c r="D21" s="257" t="n"/>
+      <c r="E21" s="257" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
 </file>